--- a/output/tables/univariable_logistic_regression_results.xlsx
+++ b/output/tables/univariable_logistic_regression_results.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="univariable_logistic_table_co" sheetId="1" r:id="rId1"/>
     <sheet name="univariable_logistic_table_im" sheetId="2" r:id="rId2"/>
+    <sheet name="univariable_logistic_table_un" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +838,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -898,7 +899,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.81, 1.11</t>
+          <t>0.81, 1.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -986,12 +987,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.00, 1.05</t>
+          <t>1.00, 1.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.063</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1026,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.56, 1.49</t>
+          <t>0.57, 1.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1047,7 +1048,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1057,7 +1058,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.074</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1102,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1124,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.067</t>
         </is>
       </c>
     </row>
@@ -1146,6 +1147,2565 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>0.5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E112"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>**Characteristic**</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>**N**</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>**exp(Beta)**</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>**95% CI**</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>**p-value**</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Consented By</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Personal consultee</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.54, 1.52</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>qSOFA Score</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.88, 1.69</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Suspected Infection Site</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gallbladder</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.65, 11.5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.47, 5.73</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lungs</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lungs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.57, 4.75</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Renal tract</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tonsils</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>un-specified</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.29, 3.47</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Urinary tract</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.65, 11.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Urine</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.24, 4.21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Patient Sex</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.80, 1.74</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Asian or Asian British</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Black or African or Caribbean or Black British</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.73, 10.2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.53, 3.57</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Height (m)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.21, 4.35</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.0, 1.01</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.98, 1.04</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ideal Body Weight (kg)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.99, 1.02</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Frailty Score</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.84, 1.12</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hypertension</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.85, 1.75</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.62, 1.43</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.56, 1.80</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chronic Respiratory Disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.71, 1.59</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.92, 2.06</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Peripheral Vascular Disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.59, 2.42</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cancer Diagnosis</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.27, 1.86</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chronic Liver Disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.35, 1.39</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chronic Neurological Disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.35, 1.39</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Immunosuppression</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.39, 1.21</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SpO2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.91, 1.04</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0.99, 1.04</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0.99, 1.01</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mean arterial Pressure</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.99, 1.02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GCS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.92, 1.10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.82, 1.10</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Initial NEWS2 score</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.97, 1.12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Final NEWS2 score</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.00, 1.10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.058</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Haematocrit</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.97, 1.01</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WBC (x10^9/L)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.98, 1.03</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Platelets (x10^9/L)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.00, 1.00</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sodium</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.95, 1.05</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Potassium</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.84, 1.47</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Creatinine</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.00, 1.01</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Bilirubin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0.99, 1.02</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CRP</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1.00, 1.00</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Lactate</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.00, 1.10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Procalcitonin</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.00, 1.05</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MR-proADM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.00, 1.21</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0.058</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Baseline StO2 level</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.96, 1.00</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.081</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Nadir of StO2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.97, 1.01</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Rate of deoxygenation (%/sec)...48</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.11, 29.7</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Rate of reoxygenation (%/sec)...49</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.76, 1.28</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Peak StO2 post vascular occlusion (%)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0.97, 1.01</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Time taken to reach baseline StO2 (secs)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.00, 1.00</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Vascular Occlusion Time...52</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0.97, 1.01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Microvascular flox index...53</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.53, 1.43</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Total vessel density (mm/mm^-2)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0.90, 1.10</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Perfused vessel density (mm/mm^-2)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0.85, 1.08</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Rate of deoxygenation (%/sec)...56</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0.23, 44.9</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Rate of reoxygenation (%/sec)...57</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0.60, 1.01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Peak StO2 post VOT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0.97, 1.00</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Time taken to reach baseline StO2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0.99, 1.00</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Microvascular flox index...61</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0.59, 1.01</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0.074</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Total vessel density</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0.90, 1.16</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Perfused vessel density</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0.87, 1.04</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0.08, 1.43</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PaO2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0.96, 1.13</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PaCO2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0.85, 1.18</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>IV Fluid Y/N</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0.86, 1.95</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Antibiotics in ED Y/N</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0.82, 2.57</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Final Diagnosis</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Acute exacerbation of asthma</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Adverse drug reaction</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Alcohol excess, metabolic acidosis</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cholangitis</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0.30, 3.28</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>COPD</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Covid-19 pneumonitis, pneumonia</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>E coli bacteraemia, ureteric obstruction and infection</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Exacerbation of COPD</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Glandular fever</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Infection of unknown origin</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Influenza A</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Left lower lobe pneumonia</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Lung adenocarcinoa / Stroke / Covid-19</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0.69, 10.7</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Pneumonia</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0.63, 4.99</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Septic shock from RML pneumonia</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0.69, 10.7</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Streptococcal bacteraemia from liver abscess</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.69, 10.7</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Urinary Tract Infection</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.69, 10.7</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Viral pneumonia</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0.25, 3.94</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Viral pneumonitis</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.69, 10.7</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Did the Patient Have Sepsis Y/N</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1.29, 2.38</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>When Did the Patient Exit the Study?</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1.00, 1.00</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0.7</t>
         </is>
       </c>
     </row>

--- a/output/tables/univariable_logistic_regression_results.xlsx
+++ b/output/tables/univariable_logistic_regression_results.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -477,51 +477,51 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.82, 1.10</t>
+          <t>0.99, 1.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCS</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.92, 1.10</t>
+          <t>0.82, 1.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>&gt;0.9</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRP</t>
+          <t>GCS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -536,19 +536,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00, 1.00</t>
+          <t>0.92, 1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>&gt;0.9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lactate</t>
+          <t>CRP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -558,186 +558,186 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.00, 1.10</t>
+          <t>1.00, 1.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Procalcitonin</t>
+          <t>Lactate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.00, 1.05</t>
+          <t>1.00, 1.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.087</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>Procalcitonin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.99, 1.02</t>
+          <t>1.00, 1.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.028</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Microvascular_flox_index</t>
+          <t>MRproADM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.53, 1.43</t>
+          <t>1.00, 1.21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.058</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MRproADM</t>
+          <t>Baseline_StO2_level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.00, 1.21</t>
+          <t>0.96, 1.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.081</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total_vessel_density</t>
+          <t>rate_of_deoxygenation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.90, 1.10</t>
+          <t>0.11, 29.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>&gt;0.9</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Perfused_vessel_density</t>
+          <t>Microvascular_flox_index</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.87, 1.04</t>
+          <t>0.53, 1.43</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Baseline_StO2_level</t>
+          <t>Peak StO2 post vascular occlusion (%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -747,42 +747,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.96, 1.00</t>
+          <t>0.97, 1.01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>0.081</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Peak_StO2_post_vascular_occlusion</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.97, 1.01</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -795,7 +768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -828,7 +801,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -894,17 +867,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.81, 1.12</t>
+          <t>0.80, 1.10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -987,12 +960,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.00, 1.06</t>
+          <t>1.00, 1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.036</t>
         </is>
       </c>
     </row>
@@ -1026,17 +999,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.57, 1.47</t>
+          <t>0.55, 1.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -1065,88 +1038,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total_vessel_density</t>
+          <t>rate_of_deoxygenation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.91, 1.10</t>
+          <t>0.10, 31.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>&gt;0.9</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Perfused_vessel_density</t>
+          <t>Baseline_StO2_level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.86, 1.09</t>
+          <t>0.96, 1.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Baseline_StO2_level</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.96, 1.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Peak_StO2_post_vascular_occlusion</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.97, 1.01</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.5</t>
+          <t>0.068</t>
         </is>
       </c>
     </row>
